--- a/01_timeline.xlsx
+++ b/01_timeline.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longh\Desktop\X\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zlhte\OneDrive\Desktop\X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489193C0-6FF7-4F2F-9978-B6317050A025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4338919-6D6F-4376-9091-23281F7124CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5628" yWindow="4476" windowWidth="23028" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="macro" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
   <si>
     <t>Real GDP and its components</t>
   </si>
@@ -103,9 +103,6 @@
     <t>Labor Productivity</t>
   </si>
   <si>
-    <t>Beginning of last two months in each quarter</t>
-  </si>
-  <si>
     <t>CPI</t>
   </si>
   <si>
@@ -127,17 +124,119 @@
     <t>S&amp;P capital</t>
   </si>
   <si>
-    <t>each ticker has different earning report</t>
-  </si>
-  <si>
     <t>S&amp;P Earning breakdown by revenue, net income profit margin, and o/s shares</t>
+  </si>
+  <si>
+    <t>Sector/Index reporting, but tickers report at different time</t>
+  </si>
+  <si>
+    <t>https://insight.factset.com/author/john-butters</t>
+  </si>
+  <si>
+    <t>c1</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/graph/?g=1Dph6</t>
+  </si>
+  <si>
+    <t>Fed</t>
+  </si>
+  <si>
+    <t>consumer's wealth breakdown by RE, Equities, Debt, and Deposits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2nd week of Mar, Jun, Sep, Dec, with one quarter lag. </t>
+  </si>
+  <si>
+    <t>c2</t>
+  </si>
+  <si>
+    <t>consumer's delinquency trend</t>
+  </si>
+  <si>
+    <t>2nd week of Feb, May, Aug, Nov, with one quarter lag.</t>
+  </si>
+  <si>
+    <t>Household Debt and Credit - FEDERAL RESERVE BANK of NEW YORK</t>
+  </si>
+  <si>
+    <t>consumer's leverage</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/graph/?g=1CPQl</t>
+  </si>
+  <si>
+    <t>c3</t>
+  </si>
+  <si>
+    <t>consumer's debt service ratio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3nd week of Mar, Jun, Sep, Dec, with one quarter lag. </t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/series/TDSP</t>
+  </si>
+  <si>
+    <t>c0</t>
+  </si>
+  <si>
+    <t>consumer's personal consumption expenditure</t>
+  </si>
+  <si>
+    <t>M/Q</t>
+  </si>
+  <si>
+    <t>End of each month, One month/quarter lag for M/Q</t>
+  </si>
+  <si>
+    <t>Local: \X\04_monitoring\JPAM_2025\inflation_components</t>
+  </si>
+  <si>
+    <t>Local: \X\99_economic\</t>
+  </si>
+  <si>
+    <t>Local: \X\04_monitoring\JPAM_2025\sp500_earning_sourcce</t>
+  </si>
+  <si>
+    <t>consumer's confidence index</t>
+  </si>
+  <si>
+    <t>Umich</t>
+  </si>
+  <si>
+    <t>1st of week of each month</t>
+  </si>
+  <si>
+    <t>United States Michigan Consumer Sentiment</t>
+  </si>
+  <si>
+    <t>Agg</t>
+  </si>
+  <si>
+    <t>Beginning of last two months in each Q (initial/final)</t>
+  </si>
+  <si>
+    <t>Sector</t>
+  </si>
+  <si>
+    <t>b1</t>
+  </si>
+  <si>
+    <t>Industrial Production</t>
+  </si>
+  <si>
+    <t>3nd week of each month</t>
+  </si>
+  <si>
+    <t>Local: \X\04_monitoring\JPAM_2025\industrial_production</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -145,13 +244,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -163,16 +276,23 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -451,128 +571,322 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:F7"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:H16"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="64.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="38" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="64.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="54" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B2" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>11</v>
       </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="D6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>4</v>
       </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C10" t="s">
+        <v>45</v>
+      </c>
+      <c r="D10" t="s">
         <v>9</v>
       </c>
-      <c r="D6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="E10" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" t="s">
         <v>6</v>
       </c>
-      <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
+      <c r="E11" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C13" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="G11" r:id="rId1" display="https://www.newyorkfed.org/microeconomics/hhdc/background.html" xr:uid="{7ABD0E68-817E-402B-ACF8-FE4D56554007}"/>
+    <hyperlink ref="G10" r:id="rId2" display="https://tradingeconomics.com/united-states/consumer-confidence" xr:uid="{CDD22088-A0F9-47C3-A2CC-99ED863C1E26}"/>
+    <hyperlink ref="G3" r:id="rId3" xr:uid="{5270A901-1899-4307-B0B0-C72E9E77F624}"/>
+    <hyperlink ref="G4" r:id="rId4" xr:uid="{ADFAF753-8B08-4D84-98B2-8CAE04FE9EC9}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId5"/>
 </worksheet>
 </file>
--- a/01_timeline.xlsx
+++ b/01_timeline.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zlhte\OneDrive\Desktop\X\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longh\Desktop\X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4338919-6D6F-4376-9091-23281F7124CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CF05BF-1982-45CA-8F3D-0A1BB0E10D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3792" yWindow="996" windowWidth="21444" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="macro" sheetId="1" r:id="rId1"/>
+    <sheet name="Auto" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -62,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="156">
   <si>
     <t>Real GDP and its components</t>
   </si>
@@ -157,9 +158,6 @@
     <t>2nd week of Feb, May, Aug, Nov, with one quarter lag.</t>
   </si>
   <si>
-    <t>Household Debt and Credit - FEDERAL RESERVE BANK of NEW YORK</t>
-  </si>
-  <si>
     <t>consumer's leverage</t>
   </si>
   <si>
@@ -181,24 +179,12 @@
     <t>c0</t>
   </si>
   <si>
-    <t>consumer's personal consumption expenditure</t>
-  </si>
-  <si>
     <t>M/Q</t>
   </si>
   <si>
     <t>End of each month, One month/quarter lag for M/Q</t>
   </si>
   <si>
-    <t>Local: \X\04_monitoring\JPAM_2025\inflation_components</t>
-  </si>
-  <si>
-    <t>Local: \X\99_economic\</t>
-  </si>
-  <si>
-    <t>Local: \X\04_monitoring\JPAM_2025\sp500_earning_sourcce</t>
-  </si>
-  <si>
     <t>consumer's confidence index</t>
   </si>
   <si>
@@ -223,20 +209,335 @@
     <t>b1</t>
   </si>
   <si>
-    <t>Industrial Production</t>
-  </si>
-  <si>
     <t>3nd week of each month</t>
   </si>
   <si>
-    <t>Local: \X\04_monitoring\JPAM_2025\industrial_production</t>
+    <t>g1</t>
+  </si>
+  <si>
+    <t>CPI / Auto</t>
+  </si>
+  <si>
+    <t>Industrial Production/ Tech || Auto || Energy&amp;Power</t>
+  </si>
+  <si>
+    <t>Auto industries</t>
+  </si>
+  <si>
+    <t>NAICS</t>
+  </si>
+  <si>
+    <t>Retail: New Car Dealer</t>
+  </si>
+  <si>
+    <t>Retail: Used Car Dealer</t>
+  </si>
+  <si>
+    <t>Manufacturer/Distributor: Auto Parts</t>
+  </si>
+  <si>
+    <t>Retail: Auto Parts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufacturer: Auto Vehicle </t>
+  </si>
+  <si>
+    <t>Examples</t>
+  </si>
+  <si>
+    <t>Finance: Auto Insurance</t>
+  </si>
+  <si>
+    <t>Finance: Auto Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABG </t>
+  </si>
+  <si>
+    <t>CVNA</t>
+  </si>
+  <si>
+    <t>AZO</t>
+  </si>
+  <si>
+    <t>CPRT</t>
+  </si>
+  <si>
+    <t>PGR</t>
+  </si>
+  <si>
+    <t>ALLY</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>PCE</t>
+  </si>
+  <si>
+    <t>×</t>
+  </si>
+  <si>
+    <t>Delinquency</t>
+  </si>
+  <si>
+    <t>['Motor_vehicles_and_parts_NAICS=3361-3"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Aerospace_and_miscellaneous_transportation_eq._NAICS=3364-9"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Motor_vehicle_NAICS=3361"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Motor_vehicle_parts_NAICS=3363"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Transportation_equipment_NAICS=336"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Automobile_and_light_duty_motor_vehicle_NAICS=33611"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Automobile_NAICS=336111"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Light_truck_and_utility_vehicle_NAICS=336112"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Heavy_duty_truck_NAICS=33612"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Motor_vehicle_body_and_trailer_NAICS=3362"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Truck_trailer_NAICS=336212"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Motor_home_NAICS=336213"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Travel_trailer_and_camper_NAICS=336214"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Aerospace_product_and_parts_NAICS=3364"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Aircraft_and_parts_NAICS=336411-3"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Railroad_eq.,_ships_and_boats,_and_other_transportation_equipment_NAICS=3365-9"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Railroad_rolling_stock_NAICS=3365"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Ship_and_boat_building_NAICS=3366"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Other_transportation_equipment_NAICS=3369"',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Automobile,_business_NAICS=336111pt."',</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 'Light_trucks,_business_NAICS=336112pt."']</t>
+  </si>
+  <si>
+    <t>New vehicles</t>
+  </si>
+  <si>
+    <t>Used cars and trucks</t>
+  </si>
+  <si>
+    <t>Motor vehicle parts and equipment</t>
+  </si>
+  <si>
+    <t>Tires</t>
+  </si>
+  <si>
+    <t>New cars(5)</t>
+  </si>
+  <si>
+    <t>New trucks(5)(12)</t>
+  </si>
+  <si>
+    <t>Vehicle accessories other than tires(4)</t>
+  </si>
+  <si>
+    <t>Vehicle parts and equipment other than tires(5)</t>
+  </si>
+  <si>
+    <t>Motor oil, coolant, and fluids(5)</t>
+  </si>
+  <si>
+    <t>Transportation services</t>
+  </si>
+  <si>
+    <t>Motor vehicle maintenance and repair</t>
+  </si>
+  <si>
+    <t>Motor vehicle body work</t>
+  </si>
+  <si>
+    <t>Motor vehicle maintenance and servicing</t>
+  </si>
+  <si>
+    <t>Motor vehicle insurance</t>
+  </si>
+  <si>
+    <t>Public transportation</t>
+  </si>
+  <si>
+    <t>Airline fares</t>
+  </si>
+  <si>
+    <t>Other intercity transportation</t>
+  </si>
+  <si>
+    <t>Intracity transportation</t>
+  </si>
+  <si>
+    <t>Leased cars and trucks(13)</t>
+  </si>
+  <si>
+    <t>Car and truck rental(4)</t>
+  </si>
+  <si>
+    <t>Motor vehicle repair(4)</t>
+  </si>
+  <si>
+    <t>Motor vehicle fees(4)</t>
+  </si>
+  <si>
+    <t>State motor vehicle registration and license fees(4)</t>
+  </si>
+  <si>
+    <t>Parking and other fees(4)</t>
+  </si>
+  <si>
+    <t>Parking fees and tolls(4)(5)</t>
+  </si>
+  <si>
+    <t>Ship fare(4)(5)</t>
+  </si>
+  <si>
+    <t>Intracity mass transit(5)(10)</t>
+  </si>
+  <si>
+    <t>PCE / Auto</t>
+  </si>
+  <si>
+    <t>IP from FED</t>
+  </si>
+  <si>
+    <t>CPI from BLS</t>
+  </si>
+  <si>
+    <t>PCE fromo BEA</t>
+  </si>
+  <si>
+    <t>Motor vehicle services</t>
+  </si>
+  <si>
+    <t>Other motor vehicle services (61)</t>
+  </si>
+  <si>
+    <t>(M) Motor vehicles and parts</t>
+  </si>
+  <si>
+    <t>(M) Transportation services</t>
+  </si>
+  <si>
+    <t>Life insurance (110)</t>
+  </si>
+  <si>
+    <t>Net household insurance (111)</t>
+  </si>
+  <si>
+    <t>Net health insurance (112)</t>
+  </si>
+  <si>
+    <t>(M) Insurance</t>
+  </si>
+  <si>
+    <t>(Q) New motor vehicles (55)</t>
+  </si>
+  <si>
+    <t>(Q) Net purchases of used motor vehicles (56)</t>
+  </si>
+  <si>
+    <t>(Q) Motor vehicle parts and accessories (58)</t>
+  </si>
+  <si>
+    <t>(Q) Motor vehicle maintenance and repair (60)</t>
+  </si>
+  <si>
+    <t>(Q) Net motor vehicle and other transportation insurance (116)</t>
+  </si>
+  <si>
+    <t>Daily</t>
+  </si>
+  <si>
+    <t>Me</t>
+  </si>
+  <si>
+    <t>SP500's implied correlation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Average corr. btw S&amp;P500 index and its components </t>
+  </si>
+  <si>
+    <t>Implied Correlation</t>
+  </si>
+  <si>
+    <t>Household Debt and Credit</t>
+  </si>
+  <si>
+    <t>market signals</t>
+  </si>
+  <si>
+    <t>m1</t>
+  </si>
+  <si>
+    <t>m2</t>
+  </si>
+  <si>
+    <t>Ticker</t>
+  </si>
+  <si>
+    <t>Fundamental Score / Profitability || Lev/Liquid/Funding || Operating Efficiency</t>
+  </si>
+  <si>
+    <t>Net.Income| RoA | CFO // Leverage | Curr | Shares // Margin | Asset Turnover Ratio</t>
+  </si>
+  <si>
+    <t>Local File</t>
+  </si>
+  <si>
+    <t>Local: fundamental.xslx</t>
+  </si>
+  <si>
+    <t>Local:  industrial_production</t>
+  </si>
+  <si>
+    <t>Local: inflation_components</t>
+  </si>
+  <si>
+    <t>Local: 99_economic</t>
+  </si>
+  <si>
+    <t>Local: sp500_earning_sourcce</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,8 +553,29 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Adobe Devanagari"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -263,6 +585,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -280,7 +608,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -290,6 +618,27 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -571,19 +920,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:H16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A2:H22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="64.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="54" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="71" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C2" t="s">
         <v>1</v>
       </c>
@@ -597,12 +946,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
         <v>0</v>
@@ -620,12 +969,12 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C4" t="s">
         <v>8</v>
@@ -643,12 +992,12 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C5" t="s">
         <v>12</v>
@@ -660,21 +1009,21 @@
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G5" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>9</v>
@@ -685,42 +1034,42 @@
       <c r="F6" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="H6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>4</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>3</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+      <c r="G7" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
@@ -734,42 +1083,42 @@
       <c r="F8" t="s">
         <v>21</v>
       </c>
-      <c r="G8" t="s">
-        <v>44</v>
+      <c r="G8" s="2" t="s">
+        <v>155</v>
       </c>
       <c r="H8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C10" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s">
         <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="F10" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
         <v>29</v>
@@ -784,15 +1133,15 @@
         <v>30</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
@@ -810,15 +1159,15 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
@@ -830,18 +1179,18 @@
         <v>27</v>
       </c>
       <c r="G13" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" t="s">
         <v>34</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>35</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
@@ -850,33 +1199,92 @@
         <v>25</v>
       </c>
       <c r="F14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G14" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="16" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>55</v>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C21" t="s">
+        <v>140</v>
+      </c>
+      <c r="D21" t="s">
+        <v>138</v>
+      </c>
+      <c r="E21" t="s">
+        <v>139</v>
+      </c>
+      <c r="F21" t="s">
+        <v>141</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C22" t="s">
+        <v>148</v>
+      </c>
+      <c r="D22" t="s">
+        <v>138</v>
+      </c>
+      <c r="E22" t="s">
+        <v>139</v>
+      </c>
+      <c r="F22" t="s">
+        <v>149</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -885,8 +1293,512 @@
     <hyperlink ref="G10" r:id="rId2" display="https://tradingeconomics.com/united-states/consumer-confidence" xr:uid="{CDD22088-A0F9-47C3-A2CC-99ED863C1E26}"/>
     <hyperlink ref="G3" r:id="rId3" xr:uid="{5270A901-1899-4307-B0B0-C72E9E77F624}"/>
     <hyperlink ref="G4" r:id="rId4" xr:uid="{ADFAF753-8B08-4D84-98B2-8CAE04FE9EC9}"/>
+    <hyperlink ref="H21" r:id="rId5" display="https://www.cboe.com/us/indices/implied/" xr:uid="{744279B1-6E59-4453-BDA7-411BB5613D87}"/>
+    <hyperlink ref="G21" r:id="rId6" display="\X\02_screening\02a_ETF_Cor1M_vs_3M" xr:uid="{3838A06E-09A1-49B9-91EF-7D1C0E540D4A}"/>
+    <hyperlink ref="G22" r:id="rId7" display="fundamental.xslx" xr:uid="{93E4EC6B-190E-4A42-BDFE-74770693B5CD}"/>
+    <hyperlink ref="G16" r:id="rId8" display="industrial_production" xr:uid="{15FDA271-E860-41C1-9B24-21D3F0C43CD4}"/>
+    <hyperlink ref="G6" r:id="rId9" display="Local: \X\04_monitoring\JPAM_2025\inflation_components" xr:uid="{6497ACBE-E7E4-45ED-A69B-360853D7CA1F}"/>
+    <hyperlink ref="G7" r:id="rId10" display="Local: \X\99_economic\" xr:uid="{6D483326-997D-48FE-B8C6-D4F1B83BCF7D}"/>
+    <hyperlink ref="G8" r:id="rId11" display="Local: \X\04_monitoring\JPAM_2025\sp500_earning_sourcce" xr:uid="{1FB277DF-1E4E-4FD2-8683-23994E3B9066}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId5"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId12"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C3FF644-530E-4118-B6C9-6213146544C4}">
+  <dimension ref="A1:N38"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2">
+        <v>336110</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3">
+        <v>441110</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4">
+        <v>441120</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="B5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C5">
+        <v>4231</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="E5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6">
+        <v>441330</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7">
+        <v>524126</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8">
+        <v>522220</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F8" s="8"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="11"/>
+      <c r="G10" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G11" s="9">
+        <v>4</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="M11" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+      <c r="H12" t="s">
+        <v>98</v>
+      </c>
+      <c r="N12" s="9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>75</v>
+      </c>
+      <c r="G13">
+        <v>5</v>
+      </c>
+      <c r="H13" t="s">
+        <v>99</v>
+      </c>
+      <c r="N13" s="9" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="9">
+        <v>4</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="I14" s="9"/>
+      <c r="N14" s="9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="9">
+        <v>4</v>
+      </c>
+      <c r="H15" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>79</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17" t="s">
+        <v>100</v>
+      </c>
+      <c r="M17" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>80</v>
+      </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
+      <c r="H18" t="s">
+        <v>101</v>
+      </c>
+      <c r="N18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19">
+        <v>6</v>
+      </c>
+      <c r="H19" t="s">
+        <v>102</v>
+      </c>
+      <c r="N19" s="9" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>82</v>
+      </c>
+      <c r="N20" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21">
+        <v>4</v>
+      </c>
+      <c r="H21" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="G22">
+        <v>5</v>
+      </c>
+      <c r="H22" t="s">
+        <v>112</v>
+      </c>
+      <c r="M22" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
+      <c r="G23">
+        <v>5</v>
+      </c>
+      <c r="H23" t="s">
+        <v>113</v>
+      </c>
+      <c r="N23" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" s="9">
+        <v>5</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="I24" s="9"/>
+      <c r="N24" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25">
+        <v>6</v>
+      </c>
+      <c r="H25" t="s">
+        <v>105</v>
+      </c>
+      <c r="N25" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
+      <c r="H26" t="s">
+        <v>106</v>
+      </c>
+      <c r="N26" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>89</v>
+      </c>
+      <c r="G27">
+        <v>6</v>
+      </c>
+      <c r="H27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="9">
+        <v>5</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+      <c r="H29" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>92</v>
+      </c>
+      <c r="G30">
+        <v>6</v>
+      </c>
+      <c r="H30" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>93</v>
+      </c>
+      <c r="G31">
+        <v>6</v>
+      </c>
+      <c r="H31" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="G32">
+        <v>7</v>
+      </c>
+      <c r="H32" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="33" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G34">
+        <v>6</v>
+      </c>
+      <c r="H34" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="35" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G35">
+        <v>6</v>
+      </c>
+      <c r="H35" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G36">
+        <v>7</v>
+      </c>
+      <c r="H36" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G37">
+        <v>6</v>
+      </c>
+      <c r="H37" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="38" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G38">
+        <v>7</v>
+      </c>
+      <c r="H38" t="s">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" display="https://www.tradingview.com/symbols/NYSE-GM/" xr:uid="{62AB20B8-52B2-47F8-AF54-07B38CA03C4B}"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://www.tradingview.com/symbols/NYSE-ABG/" xr:uid="{2C475800-1260-4B1B-A79D-2CD38254EE14}"/>
+    <hyperlink ref="D4" r:id="rId3" display="https://www.tradingview.com/symbols/NYSE-CVNA/" xr:uid="{24794B7C-7C6A-4CB9-A201-022EA52E8CFA}"/>
+    <hyperlink ref="D6" r:id="rId4" display="https://www.tradingview.com/symbols/NYSE-AZO/" xr:uid="{4A6C5DE5-CA03-4345-A4C5-0A2CACDEC2F3}"/>
+    <hyperlink ref="D5" r:id="rId5" display="https://www.tradingview.com/symbols/NASDAQ-CPRT/" xr:uid="{BD2B0427-A6F7-476B-9A6C-4313BB73D6FC}"/>
+    <hyperlink ref="D7" r:id="rId6" display="https://www.tradingview.com/symbols/NYSE-PGR/" xr:uid="{BA4E2A03-3B52-4174-A952-34D20ABF7221}"/>
+    <hyperlink ref="D8" r:id="rId7" display="https://www.tradingview.com/symbols/NYSE-ALLY/" xr:uid="{FECFB4FB-1A23-4173-B5C7-7555DCA5C75B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/01_timeline.xlsx
+++ b/01_timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longh\Desktop\X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CF05BF-1982-45CA-8F3D-0A1BB0E10D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BBAF071-085B-44CF-8341-28808D0CF462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3792" yWindow="996" windowWidth="21444" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="macro" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="163">
   <si>
     <t>Real GDP and its components</t>
   </si>
@@ -515,12 +515,6 @@
     <t>Net.Income| RoA | CFO // Leverage | Curr | Shares // Margin | Asset Turnover Ratio</t>
   </si>
   <si>
-    <t>Local File</t>
-  </si>
-  <si>
-    <t>Local: fundamental.xslx</t>
-  </si>
-  <si>
     <t>Local:  industrial_production</t>
   </si>
   <si>
@@ -531,6 +525,33 @@
   </si>
   <si>
     <t>Local: sp500_earning_sourcce</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticker </t>
+  </si>
+  <si>
+    <t>Short Squeeze</t>
+  </si>
+  <si>
+    <t>Bi-Weekly</t>
+  </si>
+  <si>
+    <t>FINRA</t>
+  </si>
+  <si>
+    <t>Local: 022_Anomalies_Fundamentals</t>
+  </si>
+  <si>
+    <t>Local: Cor1M_vs_3M</t>
+  </si>
+  <si>
+    <t>around 10 and 25 in each month</t>
   </si>
 </sst>
 </file>
@@ -575,18 +596,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -614,10 +629,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -630,15 +641,19 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -920,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:H22"/>
+  <dimension ref="A2:H23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
@@ -946,286 +961,299 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+    <row r="3" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11">
         <v>1</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="13" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
+    <row r="4" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="11">
         <v>2</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="13" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
+    <row r="5" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="11">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+    <row r="6" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="11">
         <v>4</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="12" t="s">
+      <c r="G6" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="11">
+        <v>4</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="11">
+        <v>6</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="G8" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="H8" s="12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+    </row>
+    <row r="10" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+    </row>
+    <row r="16" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="12" t="s">
+      <c r="C16" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="F17" s="12" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C8" t="s">
-        <v>20</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
-        <v>21</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="H8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -1234,7 +1262,7 @@
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+      <c r="A20" s="10" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1258,7 +1286,7 @@
         <v>141</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>142</v>
@@ -1284,7 +1312,27 @@
         <v>149</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>151</v>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A23" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" t="s">
+        <v>157</v>
+      </c>
+      <c r="D23" t="s">
+        <v>158</v>
+      </c>
+      <c r="E23" t="s">
+        <v>159</v>
+      </c>
+      <c r="F23" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -1295,14 +1343,13 @@
     <hyperlink ref="G4" r:id="rId4" xr:uid="{ADFAF753-8B08-4D84-98B2-8CAE04FE9EC9}"/>
     <hyperlink ref="H21" r:id="rId5" display="https://www.cboe.com/us/indices/implied/" xr:uid="{744279B1-6E59-4453-BDA7-411BB5613D87}"/>
     <hyperlink ref="G21" r:id="rId6" display="\X\02_screening\02a_ETF_Cor1M_vs_3M" xr:uid="{3838A06E-09A1-49B9-91EF-7D1C0E540D4A}"/>
-    <hyperlink ref="G22" r:id="rId7" display="fundamental.xslx" xr:uid="{93E4EC6B-190E-4A42-BDFE-74770693B5CD}"/>
-    <hyperlink ref="G16" r:id="rId8" display="industrial_production" xr:uid="{15FDA271-E860-41C1-9B24-21D3F0C43CD4}"/>
-    <hyperlink ref="G6" r:id="rId9" display="Local: \X\04_monitoring\JPAM_2025\inflation_components" xr:uid="{6497ACBE-E7E4-45ED-A69B-360853D7CA1F}"/>
-    <hyperlink ref="G7" r:id="rId10" display="Local: \X\99_economic\" xr:uid="{6D483326-997D-48FE-B8C6-D4F1B83BCF7D}"/>
-    <hyperlink ref="G8" r:id="rId11" display="Local: \X\04_monitoring\JPAM_2025\sp500_earning_sourcce" xr:uid="{1FB277DF-1E4E-4FD2-8683-23994E3B9066}"/>
+    <hyperlink ref="G16" r:id="rId7" display="industrial_production" xr:uid="{15FDA271-E860-41C1-9B24-21D3F0C43CD4}"/>
+    <hyperlink ref="G6" r:id="rId8" display="Local: \X\04_monitoring\JPAM_2025\inflation_components" xr:uid="{6497ACBE-E7E4-45ED-A69B-360853D7CA1F}"/>
+    <hyperlink ref="G7" r:id="rId9" display="Local: \X\99_economic\" xr:uid="{6D483326-997D-48FE-B8C6-D4F1B83BCF7D}"/>
+    <hyperlink ref="G8" r:id="rId10" display="Local: \X\04_monitoring\JPAM_2025\sp500_earning_sourcce" xr:uid="{1FB277DF-1E4E-4FD2-8683-23994E3B9066}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId12"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId11"/>
 </worksheet>
 </file>
 
@@ -1349,10 +1396,10 @@
       <c r="C2">
         <v>336110</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="5" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1363,13 +1410,13 @@
       <c r="C3">
         <v>441110</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="5" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1380,13 +1427,13 @@
       <c r="C4">
         <v>441120</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="5" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1397,10 +1444,10 @@
       <c r="C5">
         <v>4231</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E5" s="6"/>
+      <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
@@ -1409,13 +1456,13 @@
       <c r="C6">
         <v>441330</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="5" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1426,13 +1473,13 @@
       <c r="C7">
         <v>524126</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F7" s="7" t="s">
+      <c r="F7" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="5" t="s">
         <v>71</v>
       </c>
     </row>
@@ -1443,38 +1490,38 @@
       <c r="C8">
         <v>522220</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="7" t="s">
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="5" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="10" t="s">
+    <row r="10" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="D10" s="11"/>
-      <c r="G10" s="10" t="s">
+      <c r="D10" s="9"/>
+      <c r="G10" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="M10" s="10" t="s">
+      <c r="M10" s="8" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A11" s="9" t="s">
+      <c r="A11" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="7">
         <v>4</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="M11" s="7" t="s">
         <v>127</v>
       </c>
     </row>
@@ -1488,7 +1535,7 @@
       <c r="H12" t="s">
         <v>98</v>
       </c>
-      <c r="N12" s="9" t="s">
+      <c r="N12" s="7" t="s">
         <v>133</v>
       </c>
     </row>
@@ -1502,7 +1549,7 @@
       <c r="H13" t="s">
         <v>99</v>
       </c>
-      <c r="N13" s="9" t="s">
+      <c r="N13" s="7" t="s">
         <v>134</v>
       </c>
     </row>
@@ -1510,14 +1557,14 @@
       <c r="A14" t="s">
         <v>76</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="7">
         <v>4</v>
       </c>
-      <c r="H14" s="9" t="s">
+      <c r="H14" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="I14" s="9"/>
-      <c r="N14" s="9" t="s">
+      <c r="I14" s="7"/>
+      <c r="N14" s="7" t="s">
         <v>135</v>
       </c>
     </row>
@@ -1525,17 +1572,17 @@
       <c r="A15" t="s">
         <v>77</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="7">
         <v>4</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="H15" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="7" t="s">
         <v>78</v>
       </c>
       <c r="G16">
@@ -1583,7 +1630,7 @@
       <c r="H19" t="s">
         <v>102</v>
       </c>
-      <c r="N19" s="9" t="s">
+      <c r="N19" s="7" t="s">
         <v>136</v>
       </c>
     </row>
@@ -1638,13 +1685,13 @@
       <c r="A24" t="s">
         <v>86</v>
       </c>
-      <c r="G24" s="9">
+      <c r="G24" s="7">
         <v>5</v>
       </c>
-      <c r="H24" s="9" t="s">
+      <c r="H24" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="I24" s="9"/>
+      <c r="I24" s="7"/>
       <c r="N24" t="s">
         <v>130</v>
       </c>
@@ -1673,7 +1720,7 @@
       <c r="H26" t="s">
         <v>106</v>
       </c>
-      <c r="N26" s="9" t="s">
+      <c r="N26" s="7" t="s">
         <v>137</v>
       </c>
     </row>
@@ -1692,13 +1739,13 @@
       <c r="A28" t="s">
         <v>90</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="7">
         <v>5</v>
       </c>
-      <c r="H28" s="9" t="s">
+      <c r="H28" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="I28" s="9"/>
+      <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">

--- a/01_timeline.xlsx
+++ b/01_timeline.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longh\Desktop\X\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zlhte\OneDrive\Desktop\X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CF05BF-1982-45CA-8F3D-0A1BB0E10D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CC1827E-8E4E-4D4A-8BD8-A939B45A498B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3792" yWindow="996" windowWidth="21444" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="macro" sheetId="1" r:id="rId1"/>
-    <sheet name="Auto" sheetId="2" r:id="rId2"/>
+    <sheet name="__snloffice" sheetId="4" state="veryHidden" r:id="rId1"/>
+    <sheet name="macro" sheetId="1" r:id="rId2"/>
+    <sheet name="Auto" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="IQ_CH">110000</definedName>
@@ -63,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="160">
   <si>
     <t>Real GDP and its components</t>
   </si>
@@ -531,13 +532,25 @@
   </si>
   <si>
     <t>Local: sp500_earning_sourcce</t>
+  </si>
+  <si>
+    <t>m3</t>
+  </si>
+  <si>
+    <t>Short Squeeze</t>
+  </si>
+  <si>
+    <t>m4</t>
+  </si>
+  <si>
+    <t>允䅁䍁䅉䅁䍁䅁䅁䅁䕁䅁䅁䅉䅁䍁䅍䅒偂䙁䅣杔䵂䕁䄸兑䕂䍁䅁䅔䩂䕁䄰兓啂䅁䅁睅䅁䍁䅧䅁橁䕁䅫杔坂䕁䅅䅔䩂䕁䅑䅉䑂䕁䄸兔兂䕁䅅杔婂䍁䅁兓䕂䅁䅁䅅䅁䅁䅯䅁瑁䑁䅍䅍䕂䅁䅁睈䅁䅁䅙䅁硁䙁䅣䅁杁䅁䅁权䅁䕁䅉村䍂䍁䅳䅁䵁䅁䅁村䅁䕁䅍杣求䝁䅑兡あ䙁䅣兙あ䝁䅍䅡癁䕁䄸兤あ䝁䅷睢療䝁䅳䅉潁䑁䅁兎癁䑁䅁䅏癁䑁䅉䅍祁䑁䅑克䅁䅁䄴䅁煁䅁䅁兓穂䡁䅍兤求䡁䅉䅉䑂䡁䅉党歂䝁䅫䅤杁䙁䅉兙あ䝁䅫杢湂䅁䅁杁䅁䍁䅑䅁䵂䝁䄸睙桂䝁䅷䅉䑂䡁䅕杣祂䝁䅕杢橂䡁䅫䅉䵂䙁䅑䅁䩁䅁䅁䅋䅁䕁䅷睢橂䝁䅅䅢杁䕁䅍兤祂䡁䅉党畂䝁䅍入杁䕁䅷䅖㡂䑁䅁䅁䑁䅁䅁䅃䅁䕁䄰兔乂䅁䅁睃䅁䉁䅉䅁乂䕁䄰兔㙁䕁䄴兗呂䕁䅕䅁偁䅁䅁杅䅁䕁䄴兗呂䕁䅕杏乂䕁䄰兔䅁䉁䅅䅁十䅁䅁杔求䝁䅣兙あ䝁䅫杤求䅁䅁兄䅁䉁䅯䅁兂䡁䅉兡橂䝁䅕䅉䑂䝁䅧兙畂䝁䅣党䅁䍁䅅䅁㙁䅁䅁杕䕂䙁䄸睑卂䕁䅕䅒䩂䙁䅑睘卂䕁䅅䅖䩂䕁䄴睒時䕁䅑兑啂䕁䅕睘䡂䕁䅷睔䍂䕁䅅䅔䅁䅁䅣䅁睁䅁䅁杕䕂䙁䄸睑卂䕁䅕䅒䩂䙁䅑睘卂䕁䅅䅖䩂䕁䄴睒時䕁䅣䅔偂䕁䅉兑䵂䅁䅁允䅁䕁䅧䅁卂䕁䅑睘䑂䙁䅉兒䕂䕁䅫䅖時䙁䅣兑啂䕁䅍䅓時䕁䄸兖啂䕁䅷睔偂䕁䅳睘䕂䕁䅅䅖䙂䙁䄸睒䵂䕁䄸村䉂䕁䅷䅁䭁䅁䅁杈䅁䙁䅉䅒時䕁䅍睖偂䕁䅷睘䡂䕁䅷睔䍂䕁䅅䅔䅁䅁䅕䅁㉁䅁䅁杕䕂䙁䄸䅔䉂䙁䅍䅖時䙁䅉兒坂䕁䅫兒塂䙁䄸䅒䉂䙁䅑兒時䕁䅣䅔偂䕁䅉兑䵂䅁䅁䅃䅁䑁䅁䅁卂䕁䅑睘卂䕁䅅䅖䩂䕁䄴睒時䕁䅅睑啂䕁䅫睔佂䙁䄸睒䵂䕁䄸村䉂䕁䅷䅁䝁䅁䅁䅎䅁䙁䅍䅕時䕁䅙兓啂䕁䅍䅓時䕁䅷䅖時䕁䅍杕䙂䕁䅑兓啂䙁䄸杕䉂䙁䅑兓佂䕁䅣䅁十䅁䅁䅒䅁䙁䅍䅕時䕁䅙兓啂䕁䅍䅓時䕁䅷䅖時䕁䅍杕䙂䕁䅑兓啂䙁䄸杕䉂䙁䅑兓佂䕁䅣睘䕂䕁䅕杒䉂䙁䅕䅔啂䅁䅁䅇䅁䑁䅑䅁呂䙁䅁睘䝂䕁䅫䅖䑂䕁䅧睘䵂䙁䅑睘卂䕁䅅䅖䩂䕁䄴睒時䕁䅅睑啂䕁䅫睔佂䅁䅁䅆䅁䕁䅑䅁呂䙁䅁睘䝂䕁䅫䅖䑂䕁䅧睘䵂䙁䅑睘卂䕁䅅䅖䩂䕁䄴睒時䕁䅅睑啂䕁䅫睔佂䙁䄸䅒䙂䕁䅙兑噂䕁䅷䅖䅁䉁䅕䅁兂䅁䅁睕兂䙁䄸杒䩂䙁䅑睑䥂䙁䄸䅔啂䙁䄸杕䉂䙁䅑兓佂䕁䅣睘䑂䙁䅉兒䕂䕁䅫䅖時䙁䅣兑啂䕁䅍䅓時䕁䄸兖啂䕁䅷睔偂䕁䅳䅁慁䅁䅁䅙䅁䙁䅍䅕時䕁䅙兓啂䕁䅍䅓時䕁䅷䅖時䙁䅉兑啂䕁䅫杔䡂䙁䄸睑卂䕁䅕䅒䩂䙁䅑睘塂䕁䅅䅖䑂䕁䅧睘偂䙁䅕䅖䵂䕁䄸睔䱂䙁䄸䅒䙂䕁䅙兑噂䕁䅷䅖䅁䉁䅷䅁睁䅁䅁睕兂䙁䄸杒䩂䙁䅑睑䥂䙁䄸䅔啂䙁䄸杕䉂䙁䅑兓佂䕁䅣睘䕂䕁䅕睕䑂䅁䅁杆䅁䕁䅁䅁呂䙁䅁睘䝂䕁䅫䅖䑂䕁䅧睘䵂䙁䅑睘卂䕁䅅䅖䩂䕁䄴睒時䕁䅑兒呂䕁䅍睘䕂䕁䅕杒䉂䙁䅕䅔啂䅁䅁睆䅁䕁䅙䅁呂䙁䅁睘䝂䕁䅫䅖䑂䕁䅧睘䵂䙁䅑睘卂䕁䅅䅖䩂䕁䄴睒時䕁䅕杒䝂䕁䅕睑啂䕁䅫杖䙂䙁䄸䅉䕂䕁䅅䅖䙂䅁䅁兇䅁䙁䅙䅁呂䙁䅁睘䝂䕁䅫䅖䑂䕁䅧睘䵂䙁䅑睘卂䕁䅅䅖䩂䕁䄴睒時䕁䅕杒䝂䕁䅕睑啂䕁䅫杖䙂䙁䄸䅉䕂䕁䅅䅖䙂䙁䄸䅒䙂䕁䅙兑噂䕁䅷䅖䅁䉁䅳䅁杁䅁䅁睕兂䙁䄸䅕卂䕁䅫睑䙂䙁䄸睑䥂䕁䅅杔䡂䕁䅕䅁敁䅁䅁权䅁䙁䅣睔䵂䕁䅙䅁䅁䅁䅁䅐䅁䙁䅳䅍硁䙁䄸䅤灂䝁䄰党獂䝁䅫杢求䍁䄴䅥獂䡁䅍䅥摂䙁䅍䅡求䝁䅕䅤硁䍁䅅䅊剂䍁䅑杍䅁䉁䄰䅁婁䅁䅁䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯䅁䅁䅁䅯允䅁䅁䅯杁䅁䅁䅯睁䅁䅁䅅䅁䉁䅁䅁权䕁䅁䅁䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯䅁䅁䅁䅯兂䅁䅁䅯杁䅁䅁䅯睁䅁䅁䅅䅁䉁䅁䅁权䕁䅁䅁䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯睃䅁䅁䅯允䅁䅁䅯杁䅁䅁䅯睁䅁䅁䅅䅁䉁䅁䅁权䵁䅁䅁䍄䉁䅁䅁睁䅁䅁䅍䅄䅁䅁䅯睃䅁䅁䅯兆䅁䅁䅅䅁䉁䅁䅁权䕁䅁䅁䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯䅁䅁䅁䅯杂䅁䅁䅯杁䅁䅁䅯睁䅁䅁䅅䅁䉁䅁䅁权䕁䅁䅁䍄䉁䅁䅁睁䅁䅁䅍䅄䅁䅁䅯睃䅁䅁䅯杇䅁䅁䅅䅁䉁䅁䅁权䕁䅁䅁䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯䅁䅁䅁䅯睂䅁䅁䅯杁䅁䅁䅯睁䅁䅁䅅䅁䉁䅁䅁权䕁䅁䅁䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯䅁䅁䅁䅯䅃䅁䅁䅯杁䅁䅁䅯元䅁䅁䅅䅁䉁䅁䅁权䕁䅁䅁䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯睃䅁䅁䅯䅃䅁䅁䅯杁䅁䅁䅯元䅁䅁䅅䅁䉁䅁䅁睂䅁䅁䅁䕑浌䅑杷允䅁䅁䅕䅁䑁䅁䅷䅁䭁䅁䅁䅁䭁䅁䅯䅁䭁䅁䅉䅁䭁䅁䅍䅁䉁䅁䅁允䅁䅁䅯䅂䅁䅁杷允䅁䅁䅕䅁䑁䅁䅷䅁䭁䅁䅳䅁䭁䅁䅣䅁䭁䅁䅉䅁䭁䅁䅍䅁䉁䅁䅁允䅁䅁䅣䅁䅁䅁佁欵䵁䅉䅅䅁䙁䅁䅁睁䵁䅁䅁权䱁䅁䅁权䙁䅁䅁权䍁䅁䅁权䑁䅁䅁允䅁䅁䅅䅁䭁䅁䄰䅁䵁䅉䅅䅁䙁䅁䅁睁䵁䅁䅁权䱁䅁䅁权䝁䅁䅁权䍁䅁䅁权䑁䅁䅁允䅁䅁䅅䅁䭁䅁䄴䅁䵁䅉䅅䅁䙁䅁䅁睁䵁䅁䅁权䱁䅁䅁权䭁䅁䅁权䍁䅁䅁权䑁䅁䅁允䅁䅁䅅䅁䡁䅁䅁䅁䅃敌䅚䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯睄䅁䅁䅯允䅁䅁䅯杁䅁䅁䅯睁䅁䅁䅅䅁䉁䅁䅁权允䅁䅁䍄䉁䅁䅁兂䅁䅁䅍䅄䅁䅁䅯充䅁䅁䅯允䅁䅁䅯杁䅁䅁䅯睁䅁䅁䅅䅁䉁䅁䅁权䵁䅁䅁䍄䉁䅁䅁睁䅁䅁䅍䅄䅁䅁䅯睃䅁䅁䅯杅䅁䅁䅅䅁䉁䅁䅁权䕁䅁䅁䍄䉁䅁䅁睁䅁䅁䅍䅄䅁䅁䅯睃䅁䅁䅯䅆䅁䅁䅅䅁䉁䅁䅁权䕁䅁䅁䍄䉁䅁䅁睁䅁䅁䅍䅄䅁䅁䅯睃䅁䅁䅯兇䅁䅁䅅䅁䉁䅁䅁权䕁䅁䅁䍄䉁䅁䅁睁䅁䅁䅍䅄䅁䅁䅯睃䅁䅁䅯杆䅁䅁䅅䅁䉁䅁䅁权䕁䅁䅁䍄䉁䅁䅁睁䅁䅁䅍䅄䅁䅁䅯睃䅁䅁䅯睆䅁䅁䅅䅁䉁䅁䅁权䕁䅁䅁䍄䉁䅁䅁睂䅁䅁杷允䅁䅁䅙䅁䭁䉁䄰䅁䭁䅁䅳䅁䭁䉁䄴䅁䭁䉁䄸䅁䭁䅁䅑潁䭁䍁䅁䅁啁䭁䩨㙢奃桥瑕䅆時灤坹兢乴硸䅑䕢猯倹⽧瑱啙偁奤穃穸浭临䅆䑃晷䔱桘䍊剺䅑㌲䐷㕤煣杮䈴䅁䅁允䅁䅁䅯光䅁䅁杷允䅁䅁䅍䅁䑁䅁䅷䅁䭁䅁䅳䅁䭁䉁䅧䅁䉁䅁䅁允䅁䅁䅯䅂䅁䅁杷允䅁䅁䅍䅁䑁䅁䅷䅁䭁䅁䅳䅁䭁䉁䅳䅁䉁䅁䅁允䅁䅁䅯䅂䅁䅁杷允䅁䅁䅍䅁䑁䅁䅷䅁䭁䅁䅳䅁䭁䉁䅷䅁䉁䅁䅁允䅁䅁䅯䅂䅁䅁㴽</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -919,20 +932,35 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1445308-F7AB-40A8-84A9-6AFE1B5C1EF7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:H22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:H27"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="66.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="6.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="66.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="71" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="C2" t="s">
         <v>1</v>
       </c>
@@ -946,7 +974,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -969,7 +997,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8">
       <c r="A4" s="1">
         <v>2</v>
       </c>
@@ -992,7 +1020,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8">
       <c r="A5" s="1">
         <v>3</v>
       </c>
@@ -1015,7 +1043,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" s="4" customFormat="1">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -1041,7 +1069,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" s="4" customFormat="1">
       <c r="A7" s="3">
         <v>4</v>
       </c>
@@ -1064,7 +1092,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8">
       <c r="A8" s="1">
         <v>6</v>
       </c>
@@ -1090,7 +1118,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -1113,7 +1141,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
@@ -1136,7 +1164,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8">
       <c r="A12" s="1" t="s">
         <v>28</v>
       </c>
@@ -1159,7 +1187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8">
       <c r="A13" s="1" t="s">
         <v>28</v>
       </c>
@@ -1182,7 +1210,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8">
       <c r="A14" s="1" t="s">
         <v>33</v>
       </c>
@@ -1205,7 +1233,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" s="4" customFormat="1">
       <c r="A16" s="3" t="s">
         <v>47</v>
       </c>
@@ -1228,17 +1256,17 @@
         <v>152</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8">
       <c r="A18" s="1" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8">
       <c r="A20" s="13" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8">
       <c r="A21" s="1" t="s">
         <v>145</v>
       </c>
@@ -1264,7 +1292,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8">
       <c r="A22" s="1" t="s">
         <v>146</v>
       </c>
@@ -1285,6 +1313,51 @@
       </c>
       <c r="G22" s="2" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="C23" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="C27" s="13" t="str">
+        <f>_xll.SNL.Clients.Office.Excel.Functions.SPG("WOLF", "RD_CREDIT_RATING_GLOBAL", "Issuer Credit Rating", "Local Currency LT|0")</f>
+        <v/>
+      </c>
+      <c r="D27" s="13" t="str">
+        <f>_xll.SNL.Clients.Office.Excel.Functions.SPG("WOLF", "RD_CWOL_GLOBAL", "Issuer Credit Rating", "Local Currency LT|0")</f>
+        <v/>
+      </c>
+      <c r="E27" s="13" t="str">
+        <f>_xll.SNL.Clients.Office.Excel.Functions.SPG("WOLF", "RD_RATING_ACTION_GLOBAL", "Issuer Credit Rating", "Local Currency LT|0")</f>
+        <v/>
+      </c>
+      <c r="F27" s="13" t="str">
+        <f>_xll.SNL.Clients.Office.Excel.Functions.SPG("WOLF", "RD_LAST_REVIEW_DATE_GLOBAL", "Issuer Credit Rating", "Local Currency LT")</f>
+        <v/>
+      </c>
+      <c r="G27" s="13" t="str">
+        <f>_xll.SNL.Clients.Office.Excel.Functions.SPG("WOLF", "RD_CREDIT_RATING_DATE_GLOBAL", "Issuer Credit Rating", "Local Currency LT|0")</f>
+        <v/>
+      </c>
+      <c r="H27" s="13" t="str">
+        <f>_xll.SNL.Clients.Office.Excel.Functions.SPG("WOLF", "RD_CREDIT_WATCH_OUTLOOK_DATE_GLOBAL", "Issuer Credit Rating", "Local Currency LT|0")</f>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -1306,20 +1379,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C3FF644-530E-4118-B6C9-6213146544C4}">
   <dimension ref="A1:N38"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.77734375" customWidth="1"/>
-    <col min="4" max="4" width="10.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="3.6640625" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.7109375" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" t="s">
         <v>52</v>
       </c>
@@ -1342,7 +1415,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" ht="22.15" customHeight="1">
       <c r="B2" t="s">
         <v>58</v>
       </c>
@@ -1356,7 +1429,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:14" ht="22.15" customHeight="1">
       <c r="B3" t="s">
         <v>54</v>
       </c>
@@ -1373,7 +1446,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" ht="22.15" customHeight="1">
       <c r="B4" t="s">
         <v>55</v>
       </c>
@@ -1390,7 +1463,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:14" ht="22.15" customHeight="1">
       <c r="B5" t="s">
         <v>56</v>
       </c>
@@ -1402,7 +1475,7 @@
       </c>
       <c r="E5" s="6"/>
     </row>
-    <row r="6" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:14" ht="22.15" customHeight="1">
       <c r="B6" t="s">
         <v>57</v>
       </c>
@@ -1419,7 +1492,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:14" ht="22.15" customHeight="1">
       <c r="B7" t="s">
         <v>60</v>
       </c>
@@ -1436,7 +1509,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:14" ht="22.15" customHeight="1">
       <c r="B8" t="s">
         <v>61</v>
       </c>
@@ -1452,7 +1525,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="10" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" s="10" customFormat="1">
       <c r="A10" s="10" t="s">
         <v>122</v>
       </c>
@@ -1464,7 +1537,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14">
       <c r="A11" s="9" t="s">
         <v>73</v>
       </c>
@@ -1478,7 +1551,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
         <v>74</v>
       </c>
@@ -1492,7 +1565,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
         <v>75</v>
       </c>
@@ -1506,7 +1579,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
         <v>76</v>
       </c>
@@ -1521,7 +1594,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
         <v>77</v>
       </c>
@@ -1534,7 +1607,7 @@
       <c r="I15" s="9"/>
       <c r="J15" s="9"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14">
       <c r="A16" s="9" t="s">
         <v>78</v>
       </c>
@@ -1545,7 +1618,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -1559,7 +1632,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
         <v>80</v>
       </c>
@@ -1573,7 +1646,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
         <v>81</v>
       </c>
@@ -1587,7 +1660,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
         <v>82</v>
       </c>
@@ -1595,7 +1668,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
         <v>83</v>
       </c>
@@ -1606,7 +1679,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
         <v>84</v>
       </c>
@@ -1620,7 +1693,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
         <v>85</v>
       </c>
@@ -1634,7 +1707,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
         <v>86</v>
       </c>
@@ -1649,7 +1722,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
         <v>87</v>
       </c>
@@ -1663,7 +1736,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14">
       <c r="A26" t="s">
         <v>88</v>
       </c>
@@ -1677,7 +1750,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:14">
       <c r="A27" t="s">
         <v>89</v>
       </c>
@@ -1688,7 +1761,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
         <v>90</v>
       </c>
@@ -1700,7 +1773,7 @@
       </c>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -1711,7 +1784,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
         <v>92</v>
       </c>
@@ -1722,7 +1795,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
         <v>93</v>
       </c>
@@ -1733,7 +1806,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14">
       <c r="G32">
         <v>7</v>
       </c>
@@ -1741,7 +1814,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="33" spans="7:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="7:8">
       <c r="G33">
         <v>5</v>
       </c>
@@ -1749,7 +1822,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="34" spans="7:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="7:8">
       <c r="G34">
         <v>6</v>
       </c>
@@ -1757,7 +1830,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="7:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="7:8">
       <c r="G35">
         <v>6</v>
       </c>
@@ -1765,7 +1838,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="7:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="7:8">
       <c r="G36">
         <v>7</v>
       </c>
@@ -1773,7 +1846,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="37" spans="7:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="7:8">
       <c r="G37">
         <v>6</v>
       </c>
@@ -1781,7 +1854,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="38" spans="7:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="7:8">
       <c r="G38">
         <v>7</v>
       </c>

--- a/01_timeline.xlsx
+++ b/01_timeline.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\longh\Desktop\X\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E4DB5AB-3D44-4C60-9175-D962E6ED07E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89E234F-5EC6-4FA9-AD2C-CA29CA393E40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15360" yWindow="0" windowWidth="15360" windowHeight="16680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="macro" sheetId="1" r:id="rId1"/>
@@ -62,8 +62,116 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>longh</author>
+  </authors>
+  <commentList>
+    <comment ref="C8" authorId="0" shapeId="0" xr:uid="{60CF6652-2937-44A7-9D52-682AFEC1B4BE}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>longh:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Tech || 
+Auto || 
+Energy&amp;Power</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0" xr:uid="{282219F5-EC72-4014-B846-51AB8DBC7857}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>longh:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+by revenue, net income profit margin, and o/s shares</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{2A3CE22C-DC57-467B-B177-4DBE1E7A1B25}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>longh:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+ by RE, Equities, Debt, and Deposits</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C20" authorId="0" shapeId="0" xr:uid="{C1BC774F-FF3C-4921-AFB0-2220B7C01F82}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>longh:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Profitability || Lev/Liquid/Funding || Operating Efficiency</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="161">
   <si>
     <t>Real GDP and its components</t>
   </si>
@@ -125,9 +233,6 @@
     <t>S&amp;P capital</t>
   </si>
   <si>
-    <t>S&amp;P Earning breakdown by revenue, net income profit margin, and o/s shares</t>
-  </si>
-  <si>
     <t>Sector/Index reporting, but tickers report at different time</t>
   </si>
   <si>
@@ -143,9 +248,6 @@
     <t>Fed</t>
   </si>
   <si>
-    <t>consumer's wealth breakdown by RE, Equities, Debt, and Deposits</t>
-  </si>
-  <si>
     <t xml:space="preserve">2nd week of Mar, Jun, Sep, Dec, with one quarter lag. </t>
   </si>
   <si>
@@ -206,21 +308,12 @@
     <t>Sector</t>
   </si>
   <si>
-    <t>b1</t>
-  </si>
-  <si>
     <t>3nd week of each month</t>
   </si>
   <si>
-    <t>g1</t>
-  </si>
-  <si>
     <t>CPI / Auto</t>
   </si>
   <si>
-    <t>Industrial Production/ Tech || Auto || Energy&amp;Power</t>
-  </si>
-  <si>
     <t>Auto industries</t>
   </si>
   <si>
@@ -485,9 +578,6 @@
     <t>Me</t>
   </si>
   <si>
-    <t>SP500's implied correlation</t>
-  </si>
-  <si>
     <t xml:space="preserve">Average corr. btw S&amp;P500 index and its components </t>
   </si>
   <si>
@@ -509,27 +599,9 @@
     <t>Ticker</t>
   </si>
   <si>
-    <t>Fundamental Score / Profitability || Lev/Liquid/Funding || Operating Efficiency</t>
-  </si>
-  <si>
     <t>Net.Income| RoA | CFO // Leverage | Curr | Shares // Margin | Asset Turnover Ratio</t>
   </si>
   <si>
-    <t>Local:  industrial_production</t>
-  </si>
-  <si>
-    <t>Local: inflation_components</t>
-  </si>
-  <si>
-    <t>Local: 99_economic</t>
-  </si>
-  <si>
-    <t>Local: sp500_earning_sourcce</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>m3</t>
   </si>
   <si>
@@ -545,17 +617,50 @@
     <t>FINRA</t>
   </si>
   <si>
-    <t>Local: Cor1M_vs_3M</t>
-  </si>
-  <si>
     <t>around 10 and 25 in each month</t>
+  </si>
+  <si>
+    <t>Federal Fund Rate</t>
+  </si>
+  <si>
+    <t>https://fred.stlouisfed.org/graph/?g=1k0JC</t>
+  </si>
+  <si>
+    <t>including the forward-looking FFT</t>
+  </si>
+  <si>
+    <t>Local</t>
+  </si>
+  <si>
+    <t>S&amp;P Implied Correlation</t>
+  </si>
+  <si>
+    <t>S&amp;P Earning breakdown</t>
+  </si>
+  <si>
+    <t>consumer's wealth breakdown</t>
+  </si>
+  <si>
+    <t>Fundamental Score</t>
+  </si>
+  <si>
+    <t>Industrial Production</t>
+  </si>
+  <si>
+    <t>Momentums</t>
+  </si>
+  <si>
+    <t>Consumer Situations</t>
+  </si>
+  <si>
+    <t>x`</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -592,6 +697,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -620,7 +746,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -647,6 +773,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -927,31 +1054,54 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:H23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.21875" style="1" customWidth="1"/>
     <col min="2" max="2" width="6.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="66.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.21875" style="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="71" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="37.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="71" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C2" t="s">
-        <v>1</v>
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>149</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" t="s">
-        <v>7</v>
+        <v>24</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G2" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -959,9 +1109,9 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C3" s="12" t="s">
         <v>0</v>
       </c>
       <c r="D3" t="s">
@@ -970,11 +1120,11 @@
       <c r="E3" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
         <v>4</v>
-      </c>
-      <c r="G3" s="11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -982,9 +1132,9 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="12" t="s">
         <v>8</v>
       </c>
       <c r="D4" t="s">
@@ -993,11 +1143,11 @@
       <c r="E4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
         <v>11</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1005,9 +1155,9 @@
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>12</v>
       </c>
       <c r="D5" t="s">
@@ -1016,11 +1166,11 @@
       <c r="E5" t="s">
         <v>10</v>
       </c>
-      <c r="F5" t="s">
-        <v>45</v>
+      <c r="F5" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1028,10 +1178,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="12" t="s">
         <v>46</v>
-      </c>
-      <c r="C6" t="s">
-        <v>50</v>
       </c>
       <c r="D6" t="s">
         <v>9</v>
@@ -1039,11 +1189,11 @@
       <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" t="s">
+      <c r="F6" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G6" t="s">
         <v>14</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>151</v>
       </c>
       <c r="H6" t="s">
         <v>18</v>
@@ -1054,285 +1204,315 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" t="s">
-        <v>121</v>
+        <v>44</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>3</v>
       </c>
-      <c r="F7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G7" s="11" t="s">
+      <c r="F7" s="11" t="s">
         <v>152</v>
+      </c>
+      <c r="G7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="12" t="s">
+        <v>157</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G8" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>6</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>154</v>
+      </c>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="G9" t="s">
         <v>20</v>
       </c>
-      <c r="D8" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="H9" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="11" t="s">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1">
+        <v>7</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="H8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" t="s">
-        <v>40</v>
-      </c>
       <c r="D10" t="s">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="E10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>43</v>
+        <v>134</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G10" t="s">
+        <v>135</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>143</v>
-      </c>
+      <c r="F11" s="2"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" t="s">
-        <v>25</v>
-      </c>
-      <c r="F12" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>24</v>
+      <c r="A12" s="10" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" t="s">
-        <v>31</v>
+        <v>42</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>38</v>
       </c>
       <c r="D13" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>25</v>
-      </c>
-      <c r="F13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>32</v>
+        <v>39</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" t="s">
-        <v>34</v>
+        <v>42</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>27</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
       </c>
       <c r="E14" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="G14" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="D15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G15" t="s">
         <v>25</v>
-      </c>
-      <c r="F14" t="s">
-        <v>35</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
+        <v>42</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="D16" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E16" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" t="s">
         <v>25</v>
       </c>
-      <c r="F16" t="s">
-        <v>48</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F17" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="10" t="s">
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G17" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="D20" t="s">
+        <v>133</v>
+      </c>
+      <c r="E20" t="s">
+        <v>134</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G20" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>158</v>
+      </c>
+      <c r="D21" t="s">
+        <v>133</v>
+      </c>
+      <c r="E21" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="C22" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D21" t="s">
-        <v>138</v>
-      </c>
-      <c r="E21" t="s">
-        <v>139</v>
-      </c>
-      <c r="F21" t="s">
-        <v>141</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="D22" t="s">
         <v>146</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="E22" t="s">
         <v>147</v>
       </c>
-      <c r="C22" t="s">
+      <c r="F22" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="G22" t="s">
         <v>148</v>
-      </c>
-      <c r="D22" t="s">
-        <v>138</v>
-      </c>
-      <c r="E22" t="s">
-        <v>139</v>
-      </c>
-      <c r="F22" t="s">
-        <v>149</v>
-      </c>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="C23" t="s">
-        <v>157</v>
-      </c>
-      <c r="D23" t="s">
-        <v>158</v>
-      </c>
-      <c r="E23" t="s">
-        <v>159</v>
-      </c>
-      <c r="F23" t="s">
-        <v>161</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G11" r:id="rId1" display="https://www.newyorkfed.org/microeconomics/hhdc/background.html" xr:uid="{7ABD0E68-817E-402B-ACF8-FE4D56554007}"/>
-    <hyperlink ref="G10" r:id="rId2" display="https://tradingeconomics.com/united-states/consumer-confidence" xr:uid="{CDD22088-A0F9-47C3-A2CC-99ED863C1E26}"/>
-    <hyperlink ref="G3" r:id="rId3" xr:uid="{5270A901-1899-4307-B0B0-C72E9E77F624}"/>
-    <hyperlink ref="G4" r:id="rId4" xr:uid="{ADFAF753-8B08-4D84-98B2-8CAE04FE9EC9}"/>
-    <hyperlink ref="H21" r:id="rId5" display="https://www.cboe.com/us/indices/implied/" xr:uid="{744279B1-6E59-4453-BDA7-411BB5613D87}"/>
-    <hyperlink ref="G21" r:id="rId6" display="\X\02_screening\02a_ETF_Cor1M_vs_3M" xr:uid="{3838A06E-09A1-49B9-91EF-7D1C0E540D4A}"/>
-    <hyperlink ref="G16" r:id="rId7" display="industrial_production" xr:uid="{15FDA271-E860-41C1-9B24-21D3F0C43CD4}"/>
-    <hyperlink ref="G6" r:id="rId8" display="Local: \X\04_monitoring\JPAM_2025\inflation_components" xr:uid="{6497ACBE-E7E4-45ED-A69B-360853D7CA1F}"/>
-    <hyperlink ref="G7" r:id="rId9" display="Local: \X\99_economic\" xr:uid="{6D483326-997D-48FE-B8C6-D4F1B83BCF7D}"/>
-    <hyperlink ref="G8" r:id="rId10" display="Local: \X\04_monitoring\JPAM_2025\sp500_earning_sourcce" xr:uid="{1FB277DF-1E4E-4FD2-8683-23994E3B9066}"/>
+    <hyperlink ref="F14" r:id="rId1" display="https://www.newyorkfed.org/microeconomics/hhdc/background.html" xr:uid="{7ABD0E68-817E-402B-ACF8-FE4D56554007}"/>
+    <hyperlink ref="F13" r:id="rId2" display="https://tradingeconomics.com/united-states/consumer-confidence" xr:uid="{CDD22088-A0F9-47C3-A2CC-99ED863C1E26}"/>
+    <hyperlink ref="F3" r:id="rId3" xr:uid="{5270A901-1899-4307-B0B0-C72E9E77F624}"/>
+    <hyperlink ref="F4" r:id="rId4" xr:uid="{ADFAF753-8B08-4D84-98B2-8CAE04FE9EC9}"/>
+    <hyperlink ref="F8" r:id="rId5" xr:uid="{15FDA271-E860-41C1-9B24-21D3F0C43CD4}"/>
+    <hyperlink ref="F7" r:id="rId6" xr:uid="{6D483326-997D-48FE-B8C6-D4F1B83BCF7D}"/>
+    <hyperlink ref="F9" r:id="rId7" xr:uid="{1FB277DF-1E4E-4FD2-8683-23994E3B9066}"/>
+    <hyperlink ref="F2" r:id="rId8" xr:uid="{C0550891-D622-4BB5-8D02-DAFB59113398}"/>
+    <hyperlink ref="F5" r:id="rId9" xr:uid="{B07DC080-5E9F-4E06-866C-AAB2C1C66EDB}"/>
+    <hyperlink ref="F6" r:id="rId10" xr:uid="{6497ACBE-E7E4-45ED-A69B-360853D7CA1F}"/>
+    <hyperlink ref="H10" r:id="rId11" display="https://www.cboe.com/us/indices/implied/" xr:uid="{DB898EC2-8D45-4E3B-ABB4-49784040313A}"/>
+    <hyperlink ref="F10" r:id="rId12" display="Local" xr:uid="{0E8BC757-721A-4976-B2E7-D3D27CB055FA}"/>
+    <hyperlink ref="F20" r:id="rId13" xr:uid="{69772D0B-E80B-4D37-9B2C-D2CDCCE0E78D}"/>
+    <hyperlink ref="F21" r:id="rId14" xr:uid="{519892C7-B0C2-4847-AD92-17AC10D871A4}"/>
+    <hyperlink ref="F22" r:id="rId15" xr:uid="{A07C074D-2405-492D-9E3E-E5412C8A3032}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId11"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId16"/>
+  <legacyDrawing r:id="rId17"/>
 </worksheet>
 </file>
 
@@ -1351,416 +1531,416 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C2">
         <v>336110</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C3">
         <v>441110</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C4">
         <v>441120</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B5" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C5">
         <v>4231</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E5" s="4"/>
     </row>
     <row r="6" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B6" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C6">
         <v>441330</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C7">
         <v>524126</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="22.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B8" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C8">
         <v>522220</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="5" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D10" s="9"/>
       <c r="G10" s="8" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="G11" s="7">
         <v>4</v>
       </c>
       <c r="H11" s="7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G12">
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="N12" s="7" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G13">
         <v>5</v>
       </c>
       <c r="H13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="N13" s="7" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G14" s="7">
         <v>4</v>
       </c>
       <c r="H14" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="I14" s="7"/>
       <c r="N14" s="7" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G15" s="7">
         <v>4</v>
       </c>
       <c r="H15" s="7" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I15" s="7"/>
       <c r="J15" s="7"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="G16">
         <v>5</v>
       </c>
       <c r="H16" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G17">
         <v>5</v>
       </c>
       <c r="H17" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="M17" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G18">
         <v>6</v>
       </c>
       <c r="H18" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="N18" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G19">
         <v>6</v>
       </c>
       <c r="H19" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="N19" s="7" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="N20" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="G21">
         <v>4</v>
       </c>
       <c r="H21" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G22">
         <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="M22" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="G23">
         <v>5</v>
       </c>
       <c r="H23" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N23" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="G24" s="7">
         <v>5</v>
       </c>
       <c r="H24" s="7" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="I24" s="7"/>
       <c r="N24" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="G25">
         <v>6</v>
       </c>
       <c r="H25" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="N25" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G26">
         <v>6</v>
       </c>
       <c r="H26" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="N26" s="7" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="G27">
         <v>6</v>
       </c>
       <c r="H27" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G28" s="7">
         <v>5</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="I28" s="7"/>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G29">
         <v>5</v>
       </c>
       <c r="H29" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G30">
         <v>6</v>
       </c>
       <c r="H30" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="G31">
         <v>6</v>
       </c>
       <c r="H31" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -1768,7 +1948,7 @@
         <v>7</v>
       </c>
       <c r="H32" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
     </row>
     <row r="33" spans="7:8" x14ac:dyDescent="0.3">
@@ -1776,7 +1956,7 @@
         <v>5</v>
       </c>
       <c r="H33" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="34" spans="7:8" x14ac:dyDescent="0.3">
@@ -1784,7 +1964,7 @@
         <v>6</v>
       </c>
       <c r="H34" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="35" spans="7:8" x14ac:dyDescent="0.3">
@@ -1792,7 +1972,7 @@
         <v>6</v>
       </c>
       <c r="H35" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="7:8" x14ac:dyDescent="0.3">
@@ -1800,7 +1980,7 @@
         <v>7</v>
       </c>
       <c r="H36" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="7:8" x14ac:dyDescent="0.3">
@@ -1808,7 +1988,7 @@
         <v>6</v>
       </c>
       <c r="H37" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="7:8" x14ac:dyDescent="0.3">
@@ -1816,7 +1996,7 @@
         <v>7</v>
       </c>
       <c r="H38" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
